--- a/data/trans_bre/MCS12_SP_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 15,1</t>
+          <t>3,82; 14,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 22,42</t>
+          <t>11,74; 22,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 13,3</t>
+          <t>2,45; 13,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 13,75</t>
+          <t>3,35; 13,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 43,19</t>
+          <t>9,55; 41,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,97; 48,17</t>
+          <t>22,07; 47,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 28,96</t>
+          <t>4,62; 29,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 38,84</t>
+          <t>7,4; 37,36</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 17,95</t>
+          <t>8,74; 17,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 14,5</t>
+          <t>5,67; 14,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 12,0</t>
+          <t>3,08; 12,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 31,66</t>
+          <t>5,75; 31,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,27; 43,97</t>
+          <t>19,49; 44,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 31,43</t>
+          <t>11,29; 32,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 27,41</t>
+          <t>6,1; 28,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,36; 182,39</t>
+          <t>13,38; 179,68</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 16,1</t>
+          <t>5,51; 16,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 18,92</t>
+          <t>8,9; 19,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,51</t>
+          <t>1,27; 11,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 41,87</t>
+          <t>5,02; 39,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 39,27</t>
+          <t>11,58; 40,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,73; 44,65</t>
+          <t>18,58; 45,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 28,67</t>
+          <t>2,82; 28,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,56; 116,77</t>
+          <t>12,25; 106,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 13,46</t>
+          <t>4,53; 13,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 16,83</t>
+          <t>7,54; 16,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 9,64</t>
+          <t>0,41; 9,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 22,67</t>
+          <t>7,92; 21,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,78; 30,11</t>
+          <t>9,06; 30,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,16; 33,53</t>
+          <t>13,9; 33,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 18,69</t>
+          <t>0,73; 17,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,73; 53,76</t>
+          <t>16,46; 50,84</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,38</t>
+          <t>8,51; 13,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,29</t>
+          <t>10,49; 15,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,38</t>
+          <t>4,39; 9,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 24,88</t>
+          <t>9,23; 26,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,96; 32,03</t>
+          <t>19,18; 32,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,82; 32,26</t>
+          <t>20,81; 31,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 20,07</t>
+          <t>8,93; 19,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,65; 74,33</t>
+          <t>22,49; 83,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>8,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,4</t>
+          <t>4,56; 14,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,74; 22,32</t>
+          <t>11,0; 21,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 13,91</t>
+          <t>2,97; 13,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,2</t>
+          <t>2,84; 13,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,55; 41,37</t>
+          <t>10,76; 42,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,07; 47,39</t>
+          <t>20,82; 46,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 29,84</t>
+          <t>5,77; 29,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 37,36</t>
+          <t>6,81; 37,07</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,77</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 17,86</t>
+          <t>9,0; 18,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 14,82</t>
+          <t>5,64; 14,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 12,36</t>
+          <t>2,38; 11,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 31,64</t>
+          <t>2,98; 11,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,49; 44,14</t>
+          <t>19,59; 44,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 32,26</t>
+          <t>10,9; 31,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 28,41</t>
+          <t>4,87; 26,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 179,68</t>
+          <t>6,75; 29,9</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,96</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 16,53</t>
+          <t>5,36; 16,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 19,24</t>
+          <t>8,55; 19,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,57</t>
+          <t>1,17; 11,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 39,88</t>
+          <t>4,91; 15,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 40,12</t>
+          <t>11,73; 41,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,58; 45,56</t>
+          <t>17,94; 45,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 28,99</t>
+          <t>2,37; 28,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 106,67</t>
+          <t>11,44; 42,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 13,85</t>
+          <t>4,49; 13,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 16,46</t>
+          <t>7,61; 16,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 9,33</t>
+          <t>-0,0; 9,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 21,38</t>
+          <t>5,33; 14,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 30,8</t>
+          <t>9,07; 29,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,9; 33,31</t>
+          <t>13,71; 33,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 17,9</t>
+          <t>-0,08; 17,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,46; 50,84</t>
+          <t>11,1; 34,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,17</t>
+          <t>8,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,51</t>
+          <t>8,38; 13,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,17</t>
+          <t>10,48; 15,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,14</t>
+          <t>4,07; 8,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 26,71</t>
+          <t>6,68; 10,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 32,16</t>
+          <t>18,68; 32,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,81; 31,85</t>
+          <t>20,88; 32,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,93; 19,45</t>
+          <t>8,33; 19,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,49; 83,69</t>
+          <t>15,39; 27,09</t>
         </is>
       </c>
     </row>
